--- a/CSCI330 Group Project Task Tracker (2).xlsx
+++ b/CSCI330 Group Project Task Tracker (2).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/904877C71E702AD1/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://marietta0-my.sharepoint.com/personal/mca003_marietta_edu/Documents/Junior Year/F26/CSCI330/Group Project/Web-Design-and-Programming-GroupWork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA7DD34A-3871-4552-B4C9-0B224A20E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{DA7DD34A-3871-4552-B4C9-0B224A20E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD93DA79-E5DC-4A71-85C3-BFCC4288317A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{35008FAE-AE0E-4657-A8AE-48045A98CB38}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{35008FAE-AE0E-4657-A8AE-48045A98CB38}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
   <si>
     <t>Task</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>need to apply css</t>
+  </si>
+  <si>
+    <t>Maisee, Beatrice</t>
   </si>
 </sst>
 </file>
@@ -498,16 +501,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4840B388-0DE6-4C53-AF10-25A76A976816}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="17.6328125" customWidth="1"/>
-    <col min="4" max="4" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -524,7 +527,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -542,7 +545,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -559,7 +562,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -569,8 +572,11 @@
       <c r="C4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D4" s="2">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -588,7 +594,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -596,10 +602,13 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -607,15 +616,18 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -625,7 +637,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -642,7 +654,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -653,7 +665,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -664,7 +676,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>

--- a/CSCI330 Group Project Task Tracker (2).xlsx
+++ b/CSCI330 Group Project Task Tracker (2).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://marietta0-my.sharepoint.com/personal/mca003_marietta_edu/Documents/Junior Year/F26/CSCI330/Group Project/Web-Design-and-Programming-GroupWork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{DA7DD34A-3871-4552-B4C9-0B224A20E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD93DA79-E5DC-4A71-85C3-BFCC4288317A}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="8_{DA7DD34A-3871-4552-B4C9-0B224A20E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F6A5FAB-AFE7-47E1-ACB1-A9D1F95A9BF3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{35008FAE-AE0E-4657-A8AE-48045A98CB38}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{35008FAE-AE0E-4657-A8AE-48045A98CB38}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="41">
   <si>
     <t>Task</t>
   </si>
@@ -117,13 +117,58 @@
   </si>
   <si>
     <t>Maisee, Beatrice</t>
+  </si>
+  <si>
+    <t>MODULE TWO</t>
+  </si>
+  <si>
+    <t>Enroll Student form display</t>
+  </si>
+  <si>
+    <t>Add Instructor form display</t>
+  </si>
+  <si>
+    <t>Add Course form display</t>
+  </si>
+  <si>
+    <t>Register Course form display</t>
+  </si>
+  <si>
+    <t>Drop Course form display</t>
+  </si>
+  <si>
+    <t>Updating manuals</t>
+  </si>
+  <si>
+    <t>Update select list display for Add Course</t>
+  </si>
+  <si>
+    <t>Enroll Student validation (4 rules)</t>
+  </si>
+  <si>
+    <t>Add Instructor validation (4 rules)</t>
+  </si>
+  <si>
+    <t>Add Course validation (9 rules)</t>
+  </si>
+  <si>
+    <t>Register Course validation (6 rules)</t>
+  </si>
+  <si>
+    <t>Drop Course validation (6 rules)</t>
+  </si>
+  <si>
+    <t>Beatrice &amp; Maisee</t>
+  </si>
+  <si>
+    <t>Any updates/fixes from Module 1 grade</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,6 +184,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -148,7 +201,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -156,16 +209,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -500,10 +574,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4840B388-0DE6-4C53-AF10-25A76A976816}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
     <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
@@ -602,7 +676,7 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2">
         <v>46285</v>
@@ -616,7 +690,7 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D7" s="2">
         <v>46285</v>
@@ -630,7 +704,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D8" s="2">
         <f>DATE(2026,9,17)</f>
@@ -662,7 +736,7 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -673,7 +747,7 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -684,10 +758,198 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A13:E13"/>
+  </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C12" xr:uid="{1AE900CF-695F-49FE-919B-A3667E9EEDD6}">
       <formula1>"Not started, In progress, Completed, Stuck/need help"</formula1>
